--- a/myapp/src/assets/Asset72_Rent_Roll_Template.xlsx
+++ b/myapp/src/assets/Asset72_Rent_Roll_Template.xlsx
@@ -1,37 +1,79 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aneeshsai.m\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66308C00-F9DA-49E1-9935-A0A4466E926F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rent Roll Upload" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rent Roll Upload" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>Property Name</t>
+  </si>
+  <si>
+    <t>Unit Type</t>
+  </si>
+  <si>
+    <t>Sq Ft</t>
+  </si>
+  <si>
+    <t>Tenant Name</t>
+  </si>
+  <si>
+    <t>Lease Start Date</t>
+  </si>
+  <si>
+    <t>Lease End Date</t>
+  </si>
+  <si>
+    <t>Lease Status</t>
+  </si>
+  <si>
+    <t>In-Place Rent</t>
+  </si>
+  <si>
+    <t>Market Rent</t>
+  </si>
+  <si>
+    <t>Unit ID</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +92,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,73 +395,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Property Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Unit Number</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Unit Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sq Ft</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Tenant Name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Lease Start Date</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Lease End Date</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Lease Status</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>In-Place Rent</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Market Rent</t>
-        </is>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C70 C71 C72 C73 C74 C75 C76 C77 C78 C79 C80 C81 C82 C83 C84 C85 C86 C87 C88 C89 C90 C91 C92 C93 C94 C95 C96 C97 C98 C99 C100 C101 C102 C103 C104 C105 C106 C107 C108 C109 C110 C111 C112 C113 C114 C115 C116 C117 C118 C119 C120 C121 C122 C123 C124 C125 C126 C127 C128 C129 C130 C131 C132 C133 C134 C135 C136 C137 C138 C139 C140 C141 C142 C143 C144 C145 C146 C147 C148 C149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" sqref="C2:F2 C3:F3 C4:F4 C5:F5 C6:F6 C7:F7 C8:F8 C9:F9 C10:F10 C11:F11 C12:F12 C13:F13 C14:F14 C15:F15 C16:F16 C17:F17 C18:F18 C19:F19 C20:F20 C21:F21 C22:F22 C23:F23 C24:F24 C25:F25 C26:F26 C27:F27 C28:F28 C29:F29 C30:F30 C31:F31 C32:F32 C33:F33 C34:F34 C35:F35 C36:F36 C37:F37 C38:F38 C39:F39 C40:F40 C41:F41 C42:F42 C43:F43 C44:F44 C45:F45 C46:F46 C47:F47 C48:F48 C49:F49 C50:F50 C51:F51 C52:F52 C53:F53 C54:F54 C55:F55 C56:F56 C57:F57 C58:F58 C59:F59 C60:F60 C61:F61 C62:F62 C63:F63 C64:F64 C65:F65 C66:F66 C67:F67 C68:F68 C69:F69 C70:F70 C71:F71 C72:F72 C73:F73 C74:F74 C75:F75 C76:F76 C77:F77 C78:F78 C79:F79 C80:F80 C81:F81 C82:F82 C83:F83 C84:F84 C85:F85 C86:F86 C87:F87 C88:F88 C89:F89 C90:F90 C91:F91 C92:F92 C93:F93 C94:F94 C95:F95 C96:F96 C97:F97 C98:F98 C99:F99 C100:F100 C101:F101 C102:F102 C103:F103 C104:F104 C105:F105 C106:F106 C107:F107 C108:F108 C109:F109 C110:F110 C111:F111 C112:F112 C113:F113 C114:F114 C115:F115 C116:F116 C117:F117 C118:F118 C119:F119 C120:F120 C121:F121 C122:F122 C123:F123 C124:F124 C125:F125 C126:F126 C127:F127 C128:F128 C129:F129 C130:F130 C131:F131 C132:F132 C133:F133 C134:F134 C135:F135 C136:F136 C137:F137 C138:F138 C139:F139 C140:F140 C141:F141 C142:F142 C143:F143 C144:F144 C145:F145 C146:F146 C147:F147 C148:F148 C149:F149" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Studio,1BR,2BR,3BR,Retail,Office"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70 H71 H72 H73 H74 H75 H76 H77 H78 H79 H80 H81 H82 H83 H84 H85 H86 H87 H88 H89 H90 H91 H92 H93 H94 H95 H96 H97 H98 H99 H100 H101 H102 H103 H104 H105 H106 H107 H108 H109 H110 H111 H112 H113 H114 H115 H116 H117 H118 H119 H120 H121 H122 H123 H124 H125 H126 H127 H128 H129 H130 H131 H132 H133 H134 H135 H136 H137 H138 H139 H140 H141 H142 H143 H144 H145 H146 H147 H148 H149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Occupied,Vacant,Notice,Renewal"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/myapp/src/assets/Asset72_Rent_Roll_Template.xlsx
+++ b/myapp/src/assets/Asset72_Rent_Roll_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aneeshsai.m\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriya.m\Documents\Realestate_Frontend\myapp\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66308C00-F9DA-49E1-9935-A0A4466E926F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB395A0-2084-46D3-82E0-6C8A699FBF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rent Roll Upload" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Property Name</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>Sq Ft</t>
-  </si>
-  <si>
-    <t>Tenant Name</t>
   </si>
   <si>
     <t>Lease Start Date</t>
@@ -404,7 +401,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -416,24 +413,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J1" s="1"/>
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" sqref="C2:F2 C3:F3 C4:F4 C5:F5 C6:F6 C7:F7 C8:F8 C9:F9 C10:F10 C11:F11 C12:F12 C13:F13 C14:F14 C15:F15 C16:F16 C17:F17 C18:F18 C19:F19 C20:F20 C21:F21 C22:F22 C23:F23 C24:F24 C25:F25 C26:F26 C27:F27 C28:F28 C29:F29 C30:F30 C31:F31 C32:F32 C33:F33 C34:F34 C35:F35 C36:F36 C37:F37 C38:F38 C39:F39 C40:F40 C41:F41 C42:F42 C43:F43 C44:F44 C45:F45 C46:F46 C47:F47 C48:F48 C49:F49 C50:F50 C51:F51 C52:F52 C53:F53 C54:F54 C55:F55 C56:F56 C57:F57 C58:F58 C59:F59 C60:F60 C61:F61 C62:F62 C63:F63 C64:F64 C65:F65 C66:F66 C67:F67 C68:F68 C69:F69 C70:F70 C71:F71 C72:F72 C73:F73 C74:F74 C75:F75 C76:F76 C77:F77 C78:F78 C79:F79 C80:F80 C81:F81 C82:F82 C83:F83 C84:F84 C85:F85 C86:F86 C87:F87 C88:F88 C89:F89 C90:F90 C91:F91 C92:F92 C93:F93 C94:F94 C95:F95 C96:F96 C97:F97 C98:F98 C99:F99 C100:F100 C101:F101 C102:F102 C103:F103 C104:F104 C105:F105 C106:F106 C107:F107 C108:F108 C109:F109 C110:F110 C111:F111 C112:F112 C113:F113 C114:F114 C115:F115 C116:F116 C117:F117 C118:F118 C119:F119 C120:F120 C121:F121 C122:F122 C123:F123 C124:F124 C125:F125 C126:F126 C127:F127 C128:F128 C129:F129 C130:F130 C131:F131 C132:F132 C133:F133 C134:F134 C135:F135 C136:F136 C137:F137 C138:F138 C139:F139 C140:F140 C141:F141 C142:F142 C143:F143 C144:F144 C145:F145 C146:F146 C147:F147 C148:F148 C149:F149" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="C2:F149" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Studio,1BR,2BR,3BR,Retail,Office"</formula1>
     </dataValidation>
   </dataValidations>
